--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E3">
         <v>0</v>
